--- a/docs/finance/2026-10-02__finance__estimate__step-2-aws-hosting-range.xlsx
+++ b/docs/finance/2026-10-02__finance__estimate__step-2-aws-hosting-range.xlsx
@@ -746,7 +746,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -1448,9 +1448,9 @@
   </sheetData>
   <autoFilter ref="A4:E24"/>
   <mergeCells count="11">
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C36:E36"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C33:E33"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
@@ -1498,7 +1498,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
@@ -2201,7 +2201,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -6475,7 +6475,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
@@ -6635,7 +6635,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -7012,7 +7012,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -7994,7 +7994,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J265"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -8017,7 +8017,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Classes are current generation, On-Demand, Single-AZ, PostgreSQL, from the RDS us-east-1 price list published 2026-10-01T06:02:30Z, read 2026-10-02. Sorted by hourly price so the first row that clears CPU and connections is the cheapest. Connection cap uses advertised GiB and the published formula LEAST(bytes/9531392, 5000). Usable vCPU is vCPU times the 60% target. Fargate sizes are the Linux minimum memory for each CPU from the task size table, read 2026-10-02.</t>
+          <t>Classes are current generation, On-Demand, regional Single-AZ PostgreSQL (Location Type = AWS Region; Database Engine = PostgreSQL), from the RDS us-east-1 price list published 2026-10-01T06:02:30Z, read 2026-10-02. Outpost / Outposts SKUs are excluded. Sorted by hourly price ascending then class name so the first row that clears CPU and connections is the cheapest. Connection cap uses advertised GiB and the published formula LEAST(bytes/9531392, 5000). Usable vCPU is vCPU times the 60% target. Fargate sizes are the Linux minimum memory for each CPU from the task size table, read 2026-10-02.</t>
         </is>
       </c>
     </row>
@@ -8281,11 +8281,11 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>db.m5.large</t>
+          <t>db.t4g.large</t>
         </is>
       </c>
       <c r="B11" s="46" t="n">
-        <v>0.082</v>
+        <v>0.129</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>2</v>
@@ -8316,11 +8316,11 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>db.m7i.large</t>
+          <t>db.t3.large</t>
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.082</v>
+        <v>0.145</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>2</v>
@@ -8351,21 +8351,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>db.r5.large</t>
+          <t>db.m6g.large</t>
         </is>
       </c>
       <c r="B13" s="46" t="n">
-        <v>0.124</v>
+        <v>0.159</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F13" s="16">
@@ -8380,21 +8380,21 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>db.r7i.large</t>
+          <t>db.m7g.large</t>
         </is>
       </c>
       <c r="B14" s="46" t="n">
-        <v>0.124</v>
+        <v>0.168</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F14" s="16">
@@ -8419,11 +8419,11 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>db.t4g.large</t>
+          <t>db.m8g.large</t>
         </is>
       </c>
       <c r="B15" s="46" t="n">
-        <v>0.129</v>
+        <v>0.168</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>2</v>
@@ -8458,11 +8458,11 @@
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>db.t3.large</t>
+          <t>db.m5.large</t>
         </is>
       </c>
       <c r="B16" s="46" t="n">
-        <v>0.145</v>
+        <v>0.178</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>2</v>
@@ -8497,11 +8497,11 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>db.m6g.large</t>
+          <t>db.m6i.large</t>
         </is>
       </c>
       <c r="B17" s="46" t="n">
-        <v>0.159</v>
+        <v>0.178</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>2</v>
@@ -8526,17 +8526,17 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>db.m5.xlarge</t>
+          <t>db.m7i.large</t>
         </is>
       </c>
       <c r="B18" s="46" t="n">
-        <v>0.164</v>
+        <v>0.178</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
@@ -8555,17 +8555,17 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>db.m7i.xlarge</t>
+          <t>db.m9g.large</t>
         </is>
       </c>
       <c r="B19" s="46" t="n">
-        <v>0.164</v>
+        <v>0.183</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
@@ -8584,11 +8584,11 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>db.m7g.large</t>
+          <t>db.m6gd.large</t>
         </is>
       </c>
       <c r="B20" s="46" t="n">
-        <v>0.168</v>
+        <v>0.187</v>
       </c>
       <c r="C20" s="10" t="n">
         <v>2</v>
@@ -8613,11 +8613,11 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>db.m8g.large</t>
+          <t>db.m8gd.large</t>
         </is>
       </c>
       <c r="B21" s="46" t="n">
-        <v>0.168</v>
+        <v>0.1976</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>2</v>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F21" s="16">
@@ -8642,11 +8642,11 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>db.m6i.large</t>
+          <t>db.m5d.large</t>
         </is>
       </c>
       <c r="B22" s="46" t="n">
-        <v>0.178</v>
+        <v>0.21</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>2</v>
@@ -8671,11 +8671,11 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>db.m9g.large</t>
+          <t>db.m8a.large</t>
         </is>
       </c>
       <c r="B23" s="46" t="n">
-        <v>0.183</v>
+        <v>0.2149</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>2</v>
@@ -8700,11 +8700,11 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>db.m6gd.large</t>
+          <t>db.m6id.large</t>
         </is>
       </c>
       <c r="B24" s="46" t="n">
-        <v>0.187</v>
+        <v>0.224</v>
       </c>
       <c r="C24" s="10" t="n">
         <v>2</v>
@@ -8729,17 +8729,17 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>db.m8gd.large</t>
+          <t>db.r6g.large</t>
         </is>
       </c>
       <c r="B25" s="46" t="n">
-        <v>0.1976</v>
+        <v>0.225</v>
       </c>
       <c r="C25" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
@@ -8758,21 +8758,21 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>db.m5d.large</t>
+          <t>db.r7g.large</t>
         </is>
       </c>
       <c r="B26" s="46" t="n">
-        <v>0.21</v>
+        <v>0.239</v>
       </c>
       <c r="C26" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F26" s="16">
@@ -8787,21 +8787,21 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>db.m8a.large</t>
+          <t>db.r8g.large</t>
         </is>
       </c>
       <c r="B27" s="46" t="n">
-        <v>0.2149</v>
+        <v>0.239</v>
       </c>
       <c r="C27" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F27" s="16">
@@ -8816,21 +8816,21 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>db.m6id.large</t>
+          <t>db.r5.large</t>
         </is>
       </c>
       <c r="B28" s="46" t="n">
-        <v>0.224</v>
+        <v>0.25</v>
       </c>
       <c r="C28" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F28" s="16">
@@ -8845,11 +8845,11 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>db.r6g.large</t>
+          <t>db.r6i.large</t>
         </is>
       </c>
       <c r="B29" s="46" t="n">
-        <v>0.225</v>
+        <v>0.25</v>
       </c>
       <c r="C29" s="10" t="n">
         <v>2</v>
@@ -8874,11 +8874,11 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>db.r7g.large</t>
+          <t>db.r7i.large</t>
         </is>
       </c>
       <c r="B30" s="46" t="n">
-        <v>0.239</v>
+        <v>0.25</v>
       </c>
       <c r="C30" s="10" t="n">
         <v>2</v>
@@ -8903,11 +8903,11 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>db.r8g.large</t>
+          <t>db.r6gd.large</t>
         </is>
       </c>
       <c r="B31" s="46" t="n">
-        <v>0.239</v>
+        <v>0.257</v>
       </c>
       <c r="C31" s="10" t="n">
         <v>2</v>
@@ -8932,21 +8932,21 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>db.r5.xlarge</t>
+          <t>db.m6in.large</t>
         </is>
       </c>
       <c r="B32" s="46" t="n">
-        <v>0.248</v>
+        <v>0.258</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F32" s="16">
@@ -8961,21 +8961,21 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>db.r7i.xlarge</t>
+          <t>db.t4g.xlarge</t>
         </is>
       </c>
       <c r="B33" s="46" t="n">
-        <v>0.248</v>
+        <v>0.258</v>
       </c>
       <c r="C33" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F33" s="16">
@@ -8990,11 +8990,11 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>db.r6i.large</t>
+          <t>db.r8gd.large</t>
         </is>
       </c>
       <c r="B34" s="46" t="n">
-        <v>0.25</v>
+        <v>0.273</v>
       </c>
       <c r="C34" s="10" t="n">
         <v>2</v>
@@ -9019,11 +9019,11 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>db.r6gd.large</t>
+          <t>db.r5d.large</t>
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.257</v>
+        <v>0.286</v>
       </c>
       <c r="C35" s="10" t="n">
         <v>2</v>
@@ -9048,17 +9048,17 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>db.m6in.large</t>
+          <t>db.t3.xlarge</t>
         </is>
       </c>
       <c r="B36" s="46" t="n">
-        <v>0.258</v>
+        <v>0.29</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
@@ -9077,17 +9077,17 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>db.t4g.xlarge</t>
+          <t>db.m6idn.large</t>
         </is>
       </c>
       <c r="B37" s="46" t="n">
-        <v>0.258</v>
+        <v>0.295</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
@@ -9106,11 +9106,11 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>db.r8gd.large</t>
+          <t>db.r5b.large</t>
         </is>
       </c>
       <c r="B38" s="46" t="n">
-        <v>0.273</v>
+        <v>0.296</v>
       </c>
       <c r="C38" s="10" t="n">
         <v>2</v>
@@ -9135,11 +9135,11 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>db.r5d.large</t>
+          <t>db.r6id.large</t>
         </is>
       </c>
       <c r="B39" s="46" t="n">
-        <v>0.286</v>
+        <v>0.298</v>
       </c>
       <c r="C39" s="10" t="n">
         <v>2</v>
@@ -9164,21 +9164,21 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>db.t3.xlarge</t>
+          <t>db.r8a.large</t>
         </is>
       </c>
       <c r="B40" s="46" t="n">
-        <v>0.29</v>
+        <v>0.3019</v>
       </c>
       <c r="C40" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" s="10" t="n">
         <v>16</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F40" s="16">
@@ -9193,17 +9193,17 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>db.m6idn.large</t>
+          <t>db.m6g.xlarge</t>
         </is>
       </c>
       <c r="B41" s="46" t="n">
-        <v>0.295</v>
+        <v>0.318</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
@@ -9222,17 +9222,17 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>db.r5b.large</t>
+          <t>db.x2g.large</t>
         </is>
       </c>
       <c r="B42" s="46" t="n">
-        <v>0.296</v>
+        <v>0.326</v>
       </c>
       <c r="C42" s="10" t="n">
         <v>2</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -9251,21 +9251,21 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>db.r6id.large</t>
+          <t>db.m8g.xlarge</t>
         </is>
       </c>
       <c r="B43" s="46" t="n">
-        <v>0.298</v>
+        <v>0.336</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D43" s="10" t="n">
         <v>16</v>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F43" s="16">
@@ -9280,21 +9280,21 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>db.r8a.large</t>
+          <t>db.m7g.xlarge</t>
         </is>
       </c>
       <c r="B44" s="46" t="n">
-        <v>0.3019</v>
+        <v>0.337</v>
       </c>
       <c r="C44" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>16</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F44" s="16">
@@ -9309,21 +9309,21 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>db.m6g.xlarge</t>
+          <t>db.r6in.large</t>
         </is>
       </c>
       <c r="B45" s="46" t="n">
-        <v>0.318</v>
+        <v>0.346</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D45" s="10" t="n">
         <v>16</v>
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F45" s="16">
@@ -9338,21 +9338,21 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>db.x2g.large</t>
+          <t>db.m5.xlarge</t>
         </is>
       </c>
       <c r="B46" s="46" t="n">
-        <v>0.326</v>
+        <v>0.356</v>
       </c>
       <c r="C46" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F46" s="16">
@@ -9367,17 +9367,17 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>db.m5.2xlarge</t>
+          <t>db.m6i.xlarge</t>
         </is>
       </c>
       <c r="B47" s="46" t="n">
-        <v>0.328</v>
+        <v>0.356</v>
       </c>
       <c r="C47" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D47" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
@@ -9396,17 +9396,17 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>db.m7i.2xlarge</t>
+          <t>db.m7i.xlarge</t>
         </is>
       </c>
       <c r="B48" s="46" t="n">
-        <v>0.328</v>
+        <v>0.356</v>
       </c>
       <c r="C48" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
@@ -9425,11 +9425,11 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>db.m8g.xlarge</t>
+          <t>db.m9g.xlarge</t>
         </is>
       </c>
       <c r="B49" s="46" t="n">
-        <v>0.336</v>
+        <v>0.366</v>
       </c>
       <c r="C49" s="10" t="n">
         <v>4</v>
@@ -9454,11 +9454,11 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>db.m7g.xlarge</t>
+          <t>db.m6gd.xlarge</t>
         </is>
       </c>
       <c r="B50" s="46" t="n">
-        <v>0.337</v>
+        <v>0.373</v>
       </c>
       <c r="C50" s="10" t="n">
         <v>4</v>
@@ -9483,11 +9483,11 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>db.r6in.large</t>
+          <t>db.r6idn.large</t>
         </is>
       </c>
       <c r="B51" s="46" t="n">
-        <v>0.346</v>
+        <v>0.388</v>
       </c>
       <c r="C51" s="10" t="n">
         <v>2</v>
@@ -9512,11 +9512,11 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>db.m6i.xlarge</t>
+          <t>db.m8gd.xlarge</t>
         </is>
       </c>
       <c r="B52" s="46" t="n">
-        <v>0.356</v>
+        <v>0.3952</v>
       </c>
       <c r="C52" s="10" t="n">
         <v>4</v>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F52" s="16">
@@ -9541,11 +9541,11 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>db.m9g.xlarge</t>
+          <t>db.m5d.xlarge</t>
         </is>
       </c>
       <c r="B53" s="46" t="n">
-        <v>0.366</v>
+        <v>0.419</v>
       </c>
       <c r="C53" s="10" t="n">
         <v>4</v>
@@ -9570,11 +9570,11 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>db.m6gd.xlarge</t>
+          <t>db.m8a.xlarge</t>
         </is>
       </c>
       <c r="B54" s="46" t="n">
-        <v>0.373</v>
+        <v>0.4298</v>
       </c>
       <c r="C54" s="10" t="n">
         <v>4</v>
@@ -9599,21 +9599,21 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>db.r6idn.large</t>
+          <t>db.m6id.xlarge</t>
         </is>
       </c>
       <c r="B55" s="46" t="n">
-        <v>0.388</v>
+        <v>0.448</v>
       </c>
       <c r="C55" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D55" s="10" t="n">
         <v>16</v>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F55" s="16">
@@ -9628,17 +9628,17 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>db.m8gd.xlarge</t>
+          <t>db.r6g.xlarge</t>
         </is>
       </c>
       <c r="B56" s="46" t="n">
-        <v>0.3952</v>
+        <v>0.45</v>
       </c>
       <c r="C56" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
@@ -9657,21 +9657,21 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>db.m5d.xlarge</t>
+          <t>db.r7g.xlarge</t>
         </is>
       </c>
       <c r="B57" s="46" t="n">
-        <v>0.419</v>
+        <v>0.478</v>
       </c>
       <c r="C57" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D57" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F57" s="16">
@@ -9686,21 +9686,21 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>db.m8a.xlarge</t>
+          <t>db.r8g.xlarge</t>
         </is>
       </c>
       <c r="B58" s="46" t="n">
-        <v>0.4298</v>
+        <v>0.478</v>
       </c>
       <c r="C58" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F58" s="16">
@@ -9715,21 +9715,21 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>db.m6id.xlarge</t>
+          <t>db.r5.xlarge</t>
         </is>
       </c>
       <c r="B59" s="46" t="n">
-        <v>0.448</v>
+        <v>0.5</v>
       </c>
       <c r="C59" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D59" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F59" s="16">
@@ -9744,11 +9744,11 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>db.r6g.xlarge</t>
+          <t>db.r6i.xlarge</t>
         </is>
       </c>
       <c r="B60" s="46" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="C60" s="10" t="n">
         <v>4</v>
@@ -9773,11 +9773,11 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>db.r7g.xlarge</t>
+          <t>db.r7i.xlarge</t>
         </is>
       </c>
       <c r="B61" s="46" t="n">
-        <v>0.478</v>
+        <v>0.5</v>
       </c>
       <c r="C61" s="10" t="n">
         <v>4</v>
@@ -9802,11 +9802,11 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>db.r8g.xlarge</t>
+          <t>db.r6gd.xlarge</t>
         </is>
       </c>
       <c r="B62" s="46" t="n">
-        <v>0.478</v>
+        <v>0.514</v>
       </c>
       <c r="C62" s="10" t="n">
         <v>4</v>
@@ -9831,21 +9831,21 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>db.r5.2xlarge</t>
+          <t>db.m6in.xlarge</t>
         </is>
       </c>
       <c r="B63" s="46" t="n">
-        <v>0.496</v>
+        <v>0.516</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D63" s="10" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F63" s="16">
@@ -9860,21 +9860,21 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>db.r7i.2xlarge</t>
+          <t>db.t4g.2xlarge</t>
         </is>
       </c>
       <c r="B64" s="46" t="n">
-        <v>0.496</v>
+        <v>0.517</v>
       </c>
       <c r="C64" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F64" s="16">
@@ -9889,11 +9889,11 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>db.r6i.xlarge</t>
+          <t>db.r8gd.xlarge</t>
         </is>
       </c>
       <c r="B65" s="46" t="n">
-        <v>0.5</v>
+        <v>0.546</v>
       </c>
       <c r="C65" s="10" t="n">
         <v>4</v>
@@ -9918,11 +9918,11 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>db.r6gd.xlarge</t>
+          <t>db.r5d.xlarge</t>
         </is>
       </c>
       <c r="B66" s="46" t="n">
-        <v>0.514</v>
+        <v>0.571</v>
       </c>
       <c r="C66" s="10" t="n">
         <v>4</v>
@@ -9947,17 +9947,17 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>db.m6in.xlarge</t>
+          <t>db.t3.2xlarge</t>
         </is>
       </c>
       <c r="B67" s="46" t="n">
-        <v>0.516</v>
+        <v>0.579</v>
       </c>
       <c r="C67" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D67" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
@@ -9976,17 +9976,17 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>db.t4g.2xlarge</t>
+          <t>db.m6idn.xlarge</t>
         </is>
       </c>
       <c r="B68" s="46" t="n">
-        <v>0.517</v>
+        <v>0.59</v>
       </c>
       <c r="C68" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
@@ -10005,11 +10005,11 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>db.r8gd.xlarge</t>
+          <t>db.r5b.xlarge</t>
         </is>
       </c>
       <c r="B69" s="46" t="n">
-        <v>0.546</v>
+        <v>0.592</v>
       </c>
       <c r="C69" s="10" t="n">
         <v>4</v>
@@ -10034,11 +10034,11 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>db.r5d.xlarge</t>
+          <t>db.r6id.xlarge</t>
         </is>
       </c>
       <c r="B70" s="46" t="n">
-        <v>0.571</v>
+        <v>0.596</v>
       </c>
       <c r="C70" s="10" t="n">
         <v>4</v>
@@ -10063,21 +10063,21 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>db.t3.2xlarge</t>
+          <t>db.r8a.xlarge</t>
         </is>
       </c>
       <c r="B71" s="46" t="n">
-        <v>0.579</v>
+        <v>0.6038</v>
       </c>
       <c r="C71" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D71" s="10" t="n">
         <v>32</v>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F71" s="16">
@@ -10092,17 +10092,17 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>db.m6idn.xlarge</t>
+          <t>db.m6g.2xlarge</t>
         </is>
       </c>
       <c r="B72" s="46" t="n">
-        <v>0.59</v>
+        <v>0.636</v>
       </c>
       <c r="C72" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
@@ -10121,17 +10121,17 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>db.r5b.xlarge</t>
+          <t>db.x2g.xlarge</t>
         </is>
       </c>
       <c r="B73" s="46" t="n">
-        <v>0.592</v>
+        <v>0.652</v>
       </c>
       <c r="C73" s="10" t="n">
         <v>4</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
@@ -10150,21 +10150,21 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>db.r6id.xlarge</t>
+          <t>db.m8g.2xlarge</t>
         </is>
       </c>
       <c r="B74" s="46" t="n">
-        <v>0.596</v>
+        <v>0.672</v>
       </c>
       <c r="C74" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D74" s="10" t="n">
         <v>32</v>
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F74" s="16">
@@ -10179,21 +10179,21 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>db.r8a.xlarge</t>
+          <t>db.m7g.2xlarge</t>
         </is>
       </c>
       <c r="B75" s="46" t="n">
-        <v>0.6038</v>
+        <v>0.674</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D75" s="10" t="n">
         <v>32</v>
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F75" s="16">
@@ -10208,21 +10208,21 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>db.m6g.2xlarge</t>
+          <t>db.r6in.xlarge</t>
         </is>
       </c>
       <c r="B76" s="46" t="n">
-        <v>0.636</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="C76" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D76" s="10" t="n">
         <v>32</v>
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F76" s="16">
@@ -10237,21 +10237,21 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>db.x2g.xlarge</t>
+          <t>db.m5.2xlarge</t>
         </is>
       </c>
       <c r="B77" s="46" t="n">
-        <v>0.652</v>
+        <v>0.712</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F77" s="16">
@@ -10266,17 +10266,17 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>db.m5.4xlarge</t>
+          <t>db.m6i.2xlarge</t>
         </is>
       </c>
       <c r="B78" s="46" t="n">
-        <v>0.656</v>
+        <v>0.712</v>
       </c>
       <c r="C78" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
@@ -10295,17 +10295,17 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>db.m7i.4xlarge</t>
+          <t>db.m7i.2xlarge</t>
         </is>
       </c>
       <c r="B79" s="46" t="n">
-        <v>0.656</v>
+        <v>0.712</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
@@ -10324,11 +10324,11 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>db.m8g.2xlarge</t>
+          <t>db.m9g.2xlarge</t>
         </is>
       </c>
       <c r="B80" s="46" t="n">
-        <v>0.672</v>
+        <v>0.732</v>
       </c>
       <c r="C80" s="10" t="n">
         <v>8</v>
@@ -10353,11 +10353,11 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>db.m7g.2xlarge</t>
+          <t>db.m6gd.2xlarge</t>
         </is>
       </c>
       <c r="B81" s="46" t="n">
-        <v>0.674</v>
+        <v>0.747</v>
       </c>
       <c r="C81" s="10" t="n">
         <v>8</v>
@@ -10382,11 +10382,11 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>db.r6in.xlarge</t>
+          <t>db.r6idn.xlarge</t>
         </is>
       </c>
       <c r="B82" s="46" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.775</v>
       </c>
       <c r="C82" s="10" t="n">
         <v>4</v>
@@ -10411,11 +10411,11 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>db.m6i.2xlarge</t>
+          <t>db.m8gd.2xlarge</t>
         </is>
       </c>
       <c r="B83" s="46" t="n">
-        <v>0.712</v>
+        <v>0.7904</v>
       </c>
       <c r="C83" s="10" t="n">
         <v>8</v>
@@ -10425,7 +10425,7 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F83" s="16">
@@ -10440,11 +10440,11 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>db.m9g.2xlarge</t>
+          <t>db.m5d.2xlarge</t>
         </is>
       </c>
       <c r="B84" s="46" t="n">
-        <v>0.732</v>
+        <v>0.838</v>
       </c>
       <c r="C84" s="10" t="n">
         <v>8</v>
@@ -10469,11 +10469,11 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>db.m6gd.2xlarge</t>
+          <t>db.m8a.2xlarge</t>
         </is>
       </c>
       <c r="B85" s="46" t="n">
-        <v>0.747</v>
+        <v>0.8596</v>
       </c>
       <c r="C85" s="10" t="n">
         <v>8</v>
@@ -10498,21 +10498,21 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>db.r6idn.xlarge</t>
+          <t>db.m6id.2xlarge</t>
         </is>
       </c>
       <c r="B86" s="46" t="n">
-        <v>0.775</v>
+        <v>0.897</v>
       </c>
       <c r="C86" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D86" s="10" t="n">
         <v>32</v>
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F86" s="16">
@@ -10527,17 +10527,17 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>db.m8gd.2xlarge</t>
+          <t>db.r6g.2xlarge</t>
         </is>
       </c>
       <c r="B87" s="46" t="n">
-        <v>0.7904</v>
+        <v>0.899</v>
       </c>
       <c r="C87" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
@@ -10556,21 +10556,21 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>db.m5d.2xlarge</t>
+          <t>db.r7g.2xlarge</t>
         </is>
       </c>
       <c r="B88" s="46" t="n">
-        <v>0.838</v>
+        <v>0.956</v>
       </c>
       <c r="C88" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F88" s="16">
@@ -10585,21 +10585,21 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>db.m8a.2xlarge</t>
+          <t>db.r8g.2xlarge</t>
         </is>
       </c>
       <c r="B89" s="46" t="n">
-        <v>0.8596</v>
+        <v>0.956</v>
       </c>
       <c r="C89" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D89" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F89" s="16">
@@ -10614,21 +10614,21 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>db.m6id.2xlarge</t>
+          <t>db.r5.2xlarge</t>
         </is>
       </c>
       <c r="B90" s="46" t="n">
-        <v>0.897</v>
+        <v>1</v>
       </c>
       <c r="C90" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F90" s="16">
@@ -10643,11 +10643,11 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>db.r6g.2xlarge</t>
+          <t>db.r6i.2xlarge</t>
         </is>
       </c>
       <c r="B91" s="46" t="n">
-        <v>0.899</v>
+        <v>1</v>
       </c>
       <c r="C91" s="10" t="n">
         <v>8</v>
@@ -10672,11 +10672,11 @@
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>db.r7g.2xlarge</t>
+          <t>db.r7i.2xlarge</t>
         </is>
       </c>
       <c r="B92" s="46" t="n">
-        <v>0.956</v>
+        <v>1</v>
       </c>
       <c r="C92" s="10" t="n">
         <v>8</v>
@@ -10701,11 +10701,11 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>db.r8g.2xlarge</t>
+          <t>db.r6gd.2xlarge</t>
         </is>
       </c>
       <c r="B93" s="46" t="n">
-        <v>0.956</v>
+        <v>1.029</v>
       </c>
       <c r="C93" s="10" t="n">
         <v>8</v>
@@ -10730,21 +10730,21 @@
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>db.r5.4xlarge</t>
+          <t>db.m6in.2xlarge</t>
         </is>
       </c>
       <c r="B94" s="46" t="n">
-        <v>0.992</v>
+        <v>1.033</v>
       </c>
       <c r="C94" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F94" s="16">
@@ -10759,17 +10759,17 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>db.r7i.4xlarge</t>
+          <t>db.r8gd.2xlarge</t>
         </is>
       </c>
       <c r="B95" s="46" t="n">
-        <v>0.992</v>
+        <v>1.092</v>
       </c>
       <c r="C95" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
@@ -10788,11 +10788,11 @@
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>db.r6i.2xlarge</t>
+          <t>db.r5d.2xlarge</t>
         </is>
       </c>
       <c r="B96" s="46" t="n">
-        <v>1</v>
+        <v>1.143</v>
       </c>
       <c r="C96" s="10" t="n">
         <v>8</v>
@@ -10817,21 +10817,21 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>db.r6gd.2xlarge</t>
+          <t>db.m6idn.2xlarge</t>
         </is>
       </c>
       <c r="B97" s="46" t="n">
-        <v>1.029</v>
+        <v>1.18</v>
       </c>
       <c r="C97" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D97" s="10" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F97" s="16">
@@ -10846,21 +10846,21 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>db.m6in.2xlarge</t>
+          <t>db.r5b.2xlarge</t>
         </is>
       </c>
       <c r="B98" s="46" t="n">
-        <v>1.033</v>
+        <v>1.184</v>
       </c>
       <c r="C98" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F98" s="16">
@@ -10875,11 +10875,11 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>db.r8gd.2xlarge</t>
+          <t>db.r6id.2xlarge</t>
         </is>
       </c>
       <c r="B99" s="46" t="n">
-        <v>1.092</v>
+        <v>1.193</v>
       </c>
       <c r="C99" s="10" t="n">
         <v>8</v>
@@ -10904,11 +10904,11 @@
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>db.r5d.2xlarge</t>
+          <t>db.r8a.2xlarge</t>
         </is>
       </c>
       <c r="B100" s="46" t="n">
-        <v>1.143</v>
+        <v>1.2076</v>
       </c>
       <c r="C100" s="10" t="n">
         <v>8</v>
@@ -10933,17 +10933,17 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>db.m6idn.2xlarge</t>
+          <t>db.m6g.4xlarge</t>
         </is>
       </c>
       <c r="B101" s="46" t="n">
-        <v>1.18</v>
+        <v>1.272</v>
       </c>
       <c r="C101" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D101" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
@@ -10962,17 +10962,17 @@
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>db.r5b.2xlarge</t>
+          <t>db.x2g.2xlarge</t>
         </is>
       </c>
       <c r="B102" s="46" t="n">
-        <v>1.184</v>
+        <v>1.304</v>
       </c>
       <c r="C102" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
@@ -10991,21 +10991,21 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>db.r6id.2xlarge</t>
+          <t>db.m8g.4xlarge</t>
         </is>
       </c>
       <c r="B103" s="46" t="n">
-        <v>1.193</v>
+        <v>1.344</v>
       </c>
       <c r="C103" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D103" s="10" t="n">
         <v>64</v>
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F103" s="16">
@@ -11020,21 +11020,21 @@
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>db.r8a.2xlarge</t>
+          <t>db.m7g.4xlarge</t>
         </is>
       </c>
       <c r="B104" s="46" t="n">
-        <v>1.2076</v>
+        <v>1.348</v>
       </c>
       <c r="C104" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D104" s="10" t="n">
         <v>64</v>
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F104" s="16">
@@ -11049,21 +11049,21 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>db.m6g.4xlarge</t>
+          <t>db.r6in.2xlarge</t>
         </is>
       </c>
       <c r="B105" s="46" t="n">
-        <v>1.272</v>
+        <v>1.384</v>
       </c>
       <c r="C105" s="10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D105" s="10" t="n">
         <v>64</v>
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F105" s="16">
@@ -11078,21 +11078,21 @@
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>db.x2g.2xlarge</t>
+          <t>db.m5.4xlarge</t>
         </is>
       </c>
       <c r="B106" s="46" t="n">
-        <v>1.304</v>
+        <v>1.424</v>
       </c>
       <c r="C106" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F106" s="16">
@@ -11107,17 +11107,17 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>db.m5.8xlarge</t>
+          <t>db.m6i.4xlarge</t>
         </is>
       </c>
       <c r="B107" s="46" t="n">
-        <v>1.312</v>
+        <v>1.424</v>
       </c>
       <c r="C107" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D107" s="10" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
@@ -11136,17 +11136,17 @@
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>db.m7i.8xlarge</t>
+          <t>db.m7i.4xlarge</t>
         </is>
       </c>
       <c r="B108" s="46" t="n">
-        <v>1.312</v>
+        <v>1.424</v>
       </c>
       <c r="C108" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
@@ -11165,11 +11165,11 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>db.m8g.4xlarge</t>
+          <t>db.m9g.4xlarge</t>
         </is>
       </c>
       <c r="B109" s="46" t="n">
-        <v>1.344</v>
+        <v>1.465</v>
       </c>
       <c r="C109" s="10" t="n">
         <v>16</v>
@@ -11194,11 +11194,11 @@
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>db.m7g.4xlarge</t>
+          <t>db.m6gd.4xlarge</t>
         </is>
       </c>
       <c r="B110" s="46" t="n">
-        <v>1.348</v>
+        <v>1.493</v>
       </c>
       <c r="C110" s="10" t="n">
         <v>16</v>
@@ -11223,11 +11223,11 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>db.r6in.2xlarge</t>
+          <t>db.r6idn.2xlarge</t>
         </is>
       </c>
       <c r="B111" s="46" t="n">
-        <v>1.384</v>
+        <v>1.551</v>
       </c>
       <c r="C111" s="10" t="n">
         <v>8</v>
@@ -11252,11 +11252,11 @@
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>db.m6i.4xlarge</t>
+          <t>db.m8gd.4xlarge</t>
         </is>
       </c>
       <c r="B112" s="46" t="n">
-        <v>1.424</v>
+        <v>1.5808</v>
       </c>
       <c r="C112" s="10" t="n">
         <v>16</v>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F112" s="16">
@@ -11281,11 +11281,11 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>db.m9g.4xlarge</t>
+          <t>db.m5d.4xlarge</t>
         </is>
       </c>
       <c r="B113" s="46" t="n">
-        <v>1.465</v>
+        <v>1.676</v>
       </c>
       <c r="C113" s="10" t="n">
         <v>16</v>
@@ -11310,11 +11310,11 @@
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>db.m6gd.4xlarge</t>
+          <t>db.m8a.4xlarge</t>
         </is>
       </c>
       <c r="B114" s="46" t="n">
-        <v>1.493</v>
+        <v>1.7192</v>
       </c>
       <c r="C114" s="10" t="n">
         <v>16</v>
@@ -11339,21 +11339,21 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>db.r6idn.2xlarge</t>
+          <t>db.m6id.4xlarge</t>
         </is>
       </c>
       <c r="B115" s="46" t="n">
-        <v>1.551</v>
+        <v>1.794</v>
       </c>
       <c r="C115" s="10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D115" s="10" t="n">
         <v>64</v>
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F115" s="16">
@@ -11368,17 +11368,17 @@
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>db.m8gd.4xlarge</t>
+          <t>db.r6g.4xlarge</t>
         </is>
       </c>
       <c r="B116" s="46" t="n">
-        <v>1.5808</v>
+        <v>1.798</v>
       </c>
       <c r="C116" s="10" t="n">
         <v>16</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
@@ -11397,21 +11397,21 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>db.m5d.4xlarge</t>
+          <t>db.x2iedn.xlarge</t>
         </is>
       </c>
       <c r="B117" s="46" t="n">
-        <v>1.676</v>
+        <v>1.902</v>
       </c>
       <c r="C117" s="10" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D117" s="10" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F117" s="16">
@@ -11426,21 +11426,21 @@
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>db.m8a.4xlarge</t>
+          <t>db.r8g.4xlarge</t>
         </is>
       </c>
       <c r="B118" s="46" t="n">
-        <v>1.7192</v>
+        <v>1.912</v>
       </c>
       <c r="C118" s="10" t="n">
         <v>16</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F118" s="16">
@@ -11455,21 +11455,21 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>db.m6id.4xlarge</t>
+          <t>db.r7g.4xlarge</t>
         </is>
       </c>
       <c r="B119" s="46" t="n">
-        <v>1.794</v>
+        <v>1.913</v>
       </c>
       <c r="C119" s="10" t="n">
         <v>16</v>
       </c>
       <c r="D119" s="10" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F119" s="16">
@@ -11484,11 +11484,11 @@
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>db.r6g.4xlarge</t>
+          <t>db.r5.4xlarge</t>
         </is>
       </c>
       <c r="B120" s="46" t="n">
-        <v>1.798</v>
+        <v>2</v>
       </c>
       <c r="C120" s="10" t="n">
         <v>16</v>
@@ -11513,14 +11513,14 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>db.x2iedn.xlarge</t>
+          <t>db.r6i.4xlarge</t>
         </is>
       </c>
       <c r="B121" s="46" t="n">
-        <v>1.902</v>
+        <v>2</v>
       </c>
       <c r="C121" s="10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D121" s="10" t="n">
         <v>128</v>
@@ -11542,11 +11542,11 @@
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>db.r8g.4xlarge</t>
+          <t>db.r7i.4xlarge</t>
         </is>
       </c>
       <c r="B122" s="46" t="n">
-        <v>1.912</v>
+        <v>2</v>
       </c>
       <c r="C122" s="10" t="n">
         <v>16</v>
@@ -11571,11 +11571,11 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>db.r7g.4xlarge</t>
+          <t>db.r6gd.4xlarge</t>
         </is>
       </c>
       <c r="B123" s="46" t="n">
-        <v>1.913</v>
+        <v>2.057</v>
       </c>
       <c r="C123" s="10" t="n">
         <v>16</v>
@@ -11600,17 +11600,17 @@
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
         <is>
-          <t>db.m5.12xlarge</t>
+          <t>db.m6in.4xlarge</t>
         </is>
       </c>
       <c r="B124" s="46" t="n">
-        <v>1.968</v>
+        <v>2.066</v>
       </c>
       <c r="C124" s="10" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>192</v>
+        <v>64</v>
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
@@ -11629,21 +11629,21 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>db.m7i.12xlarge</t>
+          <t>db.r8gd.4xlarge</t>
         </is>
       </c>
       <c r="B125" s="46" t="n">
-        <v>1.968</v>
+        <v>2.184</v>
       </c>
       <c r="C125" s="10" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D125" s="10" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F125" s="16">
@@ -11658,17 +11658,17 @@
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>db.r5.8xlarge</t>
+          <t>db.r5d.4xlarge</t>
         </is>
       </c>
       <c r="B126" s="46" t="n">
-        <v>1.984</v>
+        <v>2.286</v>
       </c>
       <c r="C126" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
@@ -11687,21 +11687,21 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>db.r7i.8xlarge</t>
+          <t>db.m6idn.4xlarge</t>
         </is>
       </c>
       <c r="B127" s="46" t="n">
-        <v>1.984</v>
+        <v>2.36</v>
       </c>
       <c r="C127" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D127" s="10" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="E127" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F127" s="16">
@@ -11716,11 +11716,11 @@
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>db.r6i.4xlarge</t>
+          <t>db.r5b.4xlarge</t>
         </is>
       </c>
       <c r="B128" s="46" t="n">
-        <v>2</v>
+        <v>2.368</v>
       </c>
       <c r="C128" s="10" t="n">
         <v>16</v>
@@ -11745,11 +11745,11 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>db.r6gd.4xlarge</t>
+          <t>db.r6id.4xlarge</t>
         </is>
       </c>
       <c r="B129" s="46" t="n">
-        <v>2.057</v>
+        <v>2.386</v>
       </c>
       <c r="C129" s="10" t="n">
         <v>16</v>
@@ -11774,21 +11774,21 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>db.m6in.4xlarge</t>
+          <t>db.r8a.4xlarge</t>
         </is>
       </c>
       <c r="B130" s="46" t="n">
-        <v>2.066</v>
+        <v>2.4152</v>
       </c>
       <c r="C130" s="10" t="n">
         <v>16</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F130" s="16">
@@ -11803,21 +11803,21 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>db.r8gd.4xlarge</t>
+          <t>db.m6g.8xlarge</t>
         </is>
       </c>
       <c r="B131" s="46" t="n">
-        <v>2.184</v>
+        <v>2.544</v>
       </c>
       <c r="C131" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D131" s="10" t="n">
         <v>128</v>
       </c>
       <c r="E131" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F131" s="16">
@@ -11832,17 +11832,17 @@
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>db.r5d.4xlarge</t>
+          <t>db.x2g.4xlarge</t>
         </is>
       </c>
       <c r="B132" s="46" t="n">
-        <v>2.286</v>
+        <v>2.608</v>
       </c>
       <c r="C132" s="10" t="n">
         <v>16</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E132" s="10" t="inlineStr">
         <is>
@@ -11861,17 +11861,17 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>db.m6idn.4xlarge</t>
+          <t>db.m8g.8xlarge</t>
         </is>
       </c>
       <c r="B133" s="46" t="n">
-        <v>2.36</v>
+        <v>2.688</v>
       </c>
       <c r="C133" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D133" s="10" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="E133" s="10" t="inlineStr">
         <is>
@@ -11890,21 +11890,21 @@
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>db.r5b.4xlarge</t>
+          <t>db.m7g.8xlarge</t>
         </is>
       </c>
       <c r="B134" s="46" t="n">
-        <v>2.368</v>
+        <v>2.696</v>
       </c>
       <c r="C134" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D134" s="10" t="n">
         <v>128</v>
       </c>
       <c r="E134" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F134" s="16">
@@ -11919,11 +11919,11 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>db.r6id.4xlarge</t>
+          <t>db.r6in.4xlarge</t>
         </is>
       </c>
       <c r="B135" s="46" t="n">
-        <v>2.386</v>
+        <v>2.767</v>
       </c>
       <c r="C135" s="10" t="n">
         <v>16</v>
@@ -11948,21 +11948,21 @@
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>db.r8a.4xlarge</t>
+          <t>db.m5.8xlarge</t>
         </is>
       </c>
       <c r="B136" s="46" t="n">
-        <v>2.4152</v>
+        <v>2.848</v>
       </c>
       <c r="C136" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D136" s="10" t="n">
         <v>128</v>
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F136" s="16">
@@ -11977,11 +11977,11 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>db.m6g.8xlarge</t>
+          <t>db.m6i.8xlarge</t>
         </is>
       </c>
       <c r="B137" s="46" t="n">
-        <v>2.544</v>
+        <v>2.848</v>
       </c>
       <c r="C137" s="10" t="n">
         <v>32</v>
@@ -12006,21 +12006,21 @@
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>db.x2g.4xlarge</t>
+          <t>db.m7i.8xlarge</t>
         </is>
       </c>
       <c r="B138" s="46" t="n">
-        <v>2.608</v>
+        <v>2.848</v>
       </c>
       <c r="C138" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F138" s="16">
@@ -12035,17 +12035,17 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>db.m5.16xlarge</t>
+          <t>db.m9g.8xlarge</t>
         </is>
       </c>
       <c r="B139" s="46" t="n">
-        <v>2.624</v>
+        <v>2.93</v>
       </c>
       <c r="C139" s="10" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D139" s="10" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E139" s="10" t="inlineStr">
         <is>
@@ -12064,17 +12064,17 @@
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>db.m7i.16xlarge</t>
+          <t>db.m6gd.8xlarge</t>
         </is>
       </c>
       <c r="B140" s="46" t="n">
-        <v>2.624</v>
+        <v>2.987</v>
       </c>
       <c r="C140" s="10" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E140" s="10" t="inlineStr">
         <is>
@@ -12093,21 +12093,21 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>db.m8g.8xlarge</t>
+          <t>db.r6idn.4xlarge</t>
         </is>
       </c>
       <c r="B141" s="46" t="n">
-        <v>2.688</v>
+        <v>3.101</v>
       </c>
       <c r="C141" s="10" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D141" s="10" t="n">
         <v>128</v>
       </c>
       <c r="E141" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F141" s="16">
@@ -12122,11 +12122,11 @@
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>db.m7g.8xlarge</t>
+          <t>db.m8gd.8xlarge</t>
         </is>
       </c>
       <c r="B142" s="46" t="n">
-        <v>2.696</v>
+        <v>3.1616</v>
       </c>
       <c r="C142" s="10" t="n">
         <v>32</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="E142" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F142" s="16">
@@ -12151,21 +12151,21 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>db.r6in.4xlarge</t>
+          <t>db.m5d.8xlarge</t>
         </is>
       </c>
       <c r="B143" s="46" t="n">
-        <v>2.767</v>
+        <v>3.352</v>
       </c>
       <c r="C143" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D143" s="10" t="n">
         <v>128</v>
       </c>
       <c r="E143" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F143" s="16">
@@ -12180,11 +12180,11 @@
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>db.m6i.8xlarge</t>
+          <t>db.m8a.8xlarge</t>
         </is>
       </c>
       <c r="B144" s="46" t="n">
-        <v>2.848</v>
+        <v>3.4384</v>
       </c>
       <c r="C144" s="10" t="n">
         <v>32</v>
@@ -12209,11 +12209,11 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>db.m9g.8xlarge</t>
+          <t>db.m6id.8xlarge</t>
         </is>
       </c>
       <c r="B145" s="46" t="n">
-        <v>2.93</v>
+        <v>3.587</v>
       </c>
       <c r="C145" s="10" t="n">
         <v>32</v>
@@ -12238,17 +12238,17 @@
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>db.r5.12xlarge</t>
+          <t>db.r6g.8xlarge</t>
         </is>
       </c>
       <c r="B146" s="46" t="n">
-        <v>2.976</v>
+        <v>3.597</v>
       </c>
       <c r="C146" s="10" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
@@ -12267,17 +12267,17 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>db.r7i.12xlarge</t>
+          <t>db.x2iedn.2xlarge</t>
         </is>
       </c>
       <c r="B147" s="46" t="n">
-        <v>2.976</v>
+        <v>3.804</v>
       </c>
       <c r="C147" s="10" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D147" s="10" t="n">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
@@ -12296,17 +12296,17 @@
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>db.m6gd.8xlarge</t>
+          <t>db.m6g.12xlarge</t>
         </is>
       </c>
       <c r="B148" s="46" t="n">
-        <v>2.987</v>
+        <v>3.816</v>
       </c>
       <c r="C148" s="10" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="E148" s="10" t="inlineStr">
         <is>
@@ -12325,17 +12325,17 @@
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>db.r6idn.4xlarge</t>
+          <t>db.r8g.8xlarge</t>
         </is>
       </c>
       <c r="B149" s="46" t="n">
-        <v>3.101</v>
+        <v>3.824</v>
       </c>
       <c r="C149" s="10" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D149" s="10" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E149" s="10" t="inlineStr">
         <is>
@@ -12354,17 +12354,17 @@
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
         <is>
-          <t>db.m8gd.8xlarge</t>
+          <t>db.r7g.8xlarge</t>
         </is>
       </c>
       <c r="B150" s="46" t="n">
-        <v>3.1616</v>
+        <v>3.825</v>
       </c>
       <c r="C150" s="10" t="n">
         <v>32</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E150" s="10" t="inlineStr">
         <is>
@@ -12383,21 +12383,21 @@
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
         <is>
-          <t>db.m5d.8xlarge</t>
+          <t>db.r5.8xlarge</t>
         </is>
       </c>
       <c r="B151" s="46" t="n">
-        <v>3.352</v>
+        <v>4</v>
       </c>
       <c r="C151" s="10" t="n">
         <v>32</v>
       </c>
       <c r="D151" s="10" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E151" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F151" s="16">
@@ -12412,21 +12412,21 @@
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>db.m8a.8xlarge</t>
+          <t>db.r6i.8xlarge</t>
         </is>
       </c>
       <c r="B152" s="46" t="n">
-        <v>3.4384</v>
+        <v>4</v>
       </c>
       <c r="C152" s="10" t="n">
         <v>32</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E152" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F152" s="16">
@@ -12441,21 +12441,21 @@
     <row r="153">
       <c r="A153" s="10" t="inlineStr">
         <is>
-          <t>db.m6id.8xlarge</t>
+          <t>db.r7i.8xlarge</t>
         </is>
       </c>
       <c r="B153" s="46" t="n">
-        <v>3.587</v>
+        <v>4</v>
       </c>
       <c r="C153" s="10" t="n">
         <v>32</v>
       </c>
       <c r="D153" s="10" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F153" s="16">
@@ -12470,21 +12470,21 @@
     <row r="154">
       <c r="A154" s="10" t="inlineStr">
         <is>
-          <t>db.r6g.8xlarge</t>
+          <t>db.m8g.12xlarge</t>
         </is>
       </c>
       <c r="B154" s="46" t="n">
-        <v>3.597</v>
+        <v>4.032</v>
       </c>
       <c r="C154" s="10" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D154" s="10" t="n">
         <v>256</v>
       </c>
       <c r="E154" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F154" s="16">
@@ -12499,21 +12499,21 @@
     <row r="155">
       <c r="A155" s="10" t="inlineStr">
         <is>
-          <t>db.x2iedn.2xlarge</t>
+          <t>db.m7g.12xlarge</t>
         </is>
       </c>
       <c r="B155" s="46" t="n">
-        <v>3.804</v>
+        <v>4.044</v>
       </c>
       <c r="C155" s="10" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D155" s="10" t="n">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="E155" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F155" s="16">
@@ -12528,21 +12528,21 @@
     <row r="156">
       <c r="A156" s="10" t="inlineStr">
         <is>
-          <t>db.m6g.12xlarge</t>
+          <t>db.r6gd.8xlarge</t>
         </is>
       </c>
       <c r="B156" s="46" t="n">
-        <v>3.816</v>
+        <v>4.114</v>
       </c>
       <c r="C156" s="10" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="E156" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F156" s="16">
@@ -12557,21 +12557,21 @@
     <row r="157">
       <c r="A157" s="10" t="inlineStr">
         <is>
-          <t>db.r8g.8xlarge</t>
+          <t>db.m6in.8xlarge</t>
         </is>
       </c>
       <c r="B157" s="46" t="n">
-        <v>3.824</v>
+        <v>4.131</v>
       </c>
       <c r="C157" s="10" t="n">
         <v>32</v>
       </c>
       <c r="D157" s="10" t="n">
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F157" s="16">
@@ -12586,21 +12586,21 @@
     <row r="158">
       <c r="A158" s="10" t="inlineStr">
         <is>
-          <t>db.r7g.8xlarge</t>
+          <t>db.m5.12xlarge</t>
         </is>
       </c>
       <c r="B158" s="46" t="n">
-        <v>3.825</v>
+        <v>4.272</v>
       </c>
       <c r="C158" s="10" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="E158" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F158" s="16">
@@ -12615,17 +12615,17 @@
     <row r="159">
       <c r="A159" s="10" t="inlineStr">
         <is>
-          <t>db.m5.24xlarge</t>
+          <t>db.m6i.12xlarge</t>
         </is>
       </c>
       <c r="B159" s="46" t="n">
-        <v>3.936</v>
+        <v>4.272</v>
       </c>
       <c r="C159" s="10" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D159" s="10" t="n">
-        <v>384</v>
+        <v>192</v>
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
@@ -12644,17 +12644,17 @@
     <row r="160">
       <c r="A160" s="10" t="inlineStr">
         <is>
-          <t>db.m7i.24xlarge</t>
+          <t>db.m7i.12xlarge</t>
         </is>
       </c>
       <c r="B160" s="46" t="n">
-        <v>3.936</v>
+        <v>4.272</v>
       </c>
       <c r="C160" s="10" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D160" s="10" t="n">
-        <v>384</v>
+        <v>192</v>
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
@@ -12673,17 +12673,17 @@
     <row r="161">
       <c r="A161" s="10" t="inlineStr">
         <is>
-          <t>db.r5.16xlarge</t>
+          <t>db.r8gd.8xlarge</t>
         </is>
       </c>
       <c r="B161" s="46" t="n">
-        <v>3.968</v>
+        <v>4.368</v>
       </c>
       <c r="C161" s="10" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D161" s="10" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="E161" s="10" t="inlineStr">
         <is>
@@ -12702,21 +12702,21 @@
     <row r="162">
       <c r="A162" s="10" t="inlineStr">
         <is>
-          <t>db.r7i.16xlarge</t>
+          <t>db.m9g.12xlarge</t>
         </is>
       </c>
       <c r="B162" s="46" t="n">
-        <v>3.968</v>
+        <v>4.395</v>
       </c>
       <c r="C162" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D162" s="10" t="n">
-        <v>512</v>
+        <v>192</v>
       </c>
       <c r="E162" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F162" s="16">
@@ -12731,21 +12731,21 @@
     <row r="163">
       <c r="A163" s="10" t="inlineStr">
         <is>
-          <t>db.r6i.8xlarge</t>
+          <t>db.m6gd.12xlarge</t>
         </is>
       </c>
       <c r="B163" s="46" t="n">
-        <v>4</v>
+        <v>4.48</v>
       </c>
       <c r="C163" s="10" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D163" s="10" t="n">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="E163" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F163" s="16">
@@ -12760,21 +12760,21 @@
     <row r="164">
       <c r="A164" s="10" t="inlineStr">
         <is>
-          <t>db.m8g.12xlarge</t>
+          <t>db.r5d.8xlarge</t>
         </is>
       </c>
       <c r="B164" s="46" t="n">
-        <v>4.032</v>
+        <v>4.571</v>
       </c>
       <c r="C164" s="10" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D164" s="10" t="n">
         <v>256</v>
       </c>
       <c r="E164" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F164" s="16">
@@ -12789,17 +12789,17 @@
     <row r="165">
       <c r="A165" s="10" t="inlineStr">
         <is>
-          <t>db.m7g.12xlarge</t>
+          <t>db.m6idn.8xlarge</t>
         </is>
       </c>
       <c r="B165" s="46" t="n">
-        <v>4.044</v>
+        <v>4.72</v>
       </c>
       <c r="C165" s="10" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D165" s="10" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="E165" s="10" t="inlineStr">
         <is>
@@ -12818,11 +12818,11 @@
     <row r="166">
       <c r="A166" s="10" t="inlineStr">
         <is>
-          <t>db.r6gd.8xlarge</t>
+          <t>db.r5b.8xlarge</t>
         </is>
       </c>
       <c r="B166" s="46" t="n">
-        <v>4.114</v>
+        <v>4.736</v>
       </c>
       <c r="C166" s="10" t="n">
         <v>32</v>
@@ -12847,21 +12847,21 @@
     <row r="167">
       <c r="A167" s="10" t="inlineStr">
         <is>
-          <t>db.m6in.8xlarge</t>
+          <t>db.m8gd.12xlarge</t>
         </is>
       </c>
       <c r="B167" s="46" t="n">
-        <v>4.131</v>
+        <v>4.7424</v>
       </c>
       <c r="C167" s="10" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D167" s="10" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F167" s="16">
@@ -12876,21 +12876,21 @@
     <row r="168">
       <c r="A168" s="10" t="inlineStr">
         <is>
-          <t>db.m6i.12xlarge</t>
+          <t>db.r6id.8xlarge</t>
         </is>
       </c>
       <c r="B168" s="46" t="n">
-        <v>4.272</v>
+        <v>4.771</v>
       </c>
       <c r="C168" s="10" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D168" s="10" t="n">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="E168" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F168" s="16">
@@ -12905,11 +12905,11 @@
     <row r="169">
       <c r="A169" s="10" t="inlineStr">
         <is>
-          <t>db.r8gd.8xlarge</t>
+          <t>db.r8a.8xlarge</t>
         </is>
       </c>
       <c r="B169" s="46" t="n">
-        <v>4.368</v>
+        <v>4.8304</v>
       </c>
       <c r="C169" s="10" t="n">
         <v>32</v>
@@ -12934,11 +12934,11 @@
     <row r="170">
       <c r="A170" s="10" t="inlineStr">
         <is>
-          <t>db.m9g.12xlarge</t>
+          <t>db.m5d.12xlarge</t>
         </is>
       </c>
       <c r="B170" s="46" t="n">
-        <v>4.395</v>
+        <v>5.028</v>
       </c>
       <c r="C170" s="10" t="n">
         <v>48</v>
@@ -12963,17 +12963,17 @@
     <row r="171">
       <c r="A171" s="10" t="inlineStr">
         <is>
-          <t>db.m6gd.12xlarge</t>
+          <t>db.m6g.16xlarge</t>
         </is>
       </c>
       <c r="B171" s="46" t="n">
-        <v>4.48</v>
+        <v>5.088</v>
       </c>
       <c r="C171" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D171" s="10" t="n">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
@@ -12992,21 +12992,21 @@
     <row r="172">
       <c r="A172" s="10" t="inlineStr">
         <is>
-          <t>db.r5d.8xlarge</t>
+          <t>db.m8a.12xlarge</t>
         </is>
       </c>
       <c r="B172" s="46" t="n">
-        <v>4.571</v>
+        <v>5.1576</v>
       </c>
       <c r="C172" s="10" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D172" s="10" t="n">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="E172" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F172" s="16">
@@ -13021,21 +13021,21 @@
     <row r="173">
       <c r="A173" s="10" t="inlineStr">
         <is>
-          <t>db.m6idn.8xlarge</t>
+          <t>db.x2g.8xlarge</t>
         </is>
       </c>
       <c r="B173" s="46" t="n">
-        <v>4.72</v>
+        <v>5.216</v>
       </c>
       <c r="C173" s="10" t="n">
         <v>32</v>
       </c>
       <c r="D173" s="10" t="n">
-        <v>128</v>
+        <v>512</v>
       </c>
       <c r="E173" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F173" s="16">
@@ -13050,21 +13050,21 @@
     <row r="174">
       <c r="A174" s="10" t="inlineStr">
         <is>
-          <t>db.r5b.8xlarge</t>
+          <t>db.m8g.16xlarge</t>
         </is>
       </c>
       <c r="B174" s="46" t="n">
-        <v>4.736</v>
+        <v>5.376</v>
       </c>
       <c r="C174" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D174" s="10" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F174" s="16">
@@ -13079,11 +13079,11 @@
     <row r="175">
       <c r="A175" s="10" t="inlineStr">
         <is>
-          <t>db.m8gd.12xlarge</t>
+          <t>db.m6id.12xlarge</t>
         </is>
       </c>
       <c r="B175" s="46" t="n">
-        <v>4.7424</v>
+        <v>5.381</v>
       </c>
       <c r="C175" s="10" t="n">
         <v>48</v>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F175" s="16">
@@ -13108,21 +13108,21 @@
     <row r="176">
       <c r="A176" s="10" t="inlineStr">
         <is>
-          <t>db.r6id.8xlarge</t>
+          <t>db.m7g.16xlarge</t>
         </is>
       </c>
       <c r="B176" s="46" t="n">
-        <v>4.771</v>
+        <v>5.392</v>
       </c>
       <c r="C176" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D176" s="10" t="n">
         <v>256</v>
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F176" s="16">
@@ -13137,17 +13137,17 @@
     <row r="177">
       <c r="A177" s="10" t="inlineStr">
         <is>
-          <t>db.r8a.8xlarge</t>
+          <t>db.r6g.12xlarge</t>
         </is>
       </c>
       <c r="B177" s="46" t="n">
-        <v>4.8304</v>
+        <v>5.395</v>
       </c>
       <c r="C177" s="10" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D177" s="10" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E177" s="10" t="inlineStr">
         <is>
@@ -13166,21 +13166,21 @@
     <row r="178">
       <c r="A178" s="10" t="inlineStr">
         <is>
-          <t>db.m5d.12xlarge</t>
+          <t>db.r6in.8xlarge</t>
         </is>
       </c>
       <c r="B178" s="46" t="n">
-        <v>5.028</v>
+        <v>5.534</v>
       </c>
       <c r="C178" s="10" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D178" s="10" t="n">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="E178" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F178" s="16">
@@ -13195,11 +13195,11 @@
     <row r="179">
       <c r="A179" s="10" t="inlineStr">
         <is>
-          <t>db.m6g.16xlarge</t>
+          <t>db.m5.16xlarge</t>
         </is>
       </c>
       <c r="B179" s="46" t="n">
-        <v>5.088</v>
+        <v>5.696</v>
       </c>
       <c r="C179" s="10" t="n">
         <v>64</v>
@@ -13224,17 +13224,17 @@
     <row r="180">
       <c r="A180" s="10" t="inlineStr">
         <is>
-          <t>db.m8a.12xlarge</t>
+          <t>db.m6i.16xlarge</t>
         </is>
       </c>
       <c r="B180" s="46" t="n">
-        <v>5.1576</v>
+        <v>5.696</v>
       </c>
       <c r="C180" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D180" s="10" t="n">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="E180" s="10" t="inlineStr">
         <is>
@@ -13253,21 +13253,21 @@
     <row r="181">
       <c r="A181" s="10" t="inlineStr">
         <is>
-          <t>db.x2g.8xlarge</t>
+          <t>db.m7i.16xlarge</t>
         </is>
       </c>
       <c r="B181" s="46" t="n">
-        <v>5.216</v>
+        <v>5.696</v>
       </c>
       <c r="C181" s="10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="D181" s="10" t="n">
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="E181" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F181" s="16">
@@ -13282,21 +13282,21 @@
     <row r="182">
       <c r="A182" s="10" t="inlineStr">
         <is>
-          <t>db.m8g.16xlarge</t>
+          <t>db.r8g.12xlarge</t>
         </is>
       </c>
       <c r="B182" s="46" t="n">
-        <v>5.376</v>
+        <v>5.736</v>
       </c>
       <c r="C182" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D182" s="10" t="n">
         <v>384</v>
       </c>
       <c r="E182" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F182" s="16">
@@ -13311,21 +13311,21 @@
     <row r="183">
       <c r="A183" s="10" t="inlineStr">
         <is>
-          <t>db.m6id.12xlarge</t>
+          <t>db.r7g.12xlarge</t>
         </is>
       </c>
       <c r="B183" s="46" t="n">
-        <v>5.381</v>
+        <v>5.738</v>
       </c>
       <c r="C183" s="10" t="n">
         <v>48</v>
       </c>
       <c r="D183" s="10" t="n">
-        <v>192</v>
+        <v>384</v>
       </c>
       <c r="E183" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F183" s="16">
@@ -13340,11 +13340,11 @@
     <row r="184">
       <c r="A184" s="10" t="inlineStr">
         <is>
-          <t>db.m7g.16xlarge</t>
+          <t>db.m9g.16xlarge</t>
         </is>
       </c>
       <c r="B184" s="46" t="n">
-        <v>5.392</v>
+        <v>5.86</v>
       </c>
       <c r="C184" s="10" t="n">
         <v>64</v>
@@ -13369,21 +13369,21 @@
     <row r="185">
       <c r="A185" s="10" t="inlineStr">
         <is>
-          <t>db.r6g.12xlarge</t>
+          <t>db.m6gd.16xlarge</t>
         </is>
       </c>
       <c r="B185" s="46" t="n">
-        <v>5.395</v>
+        <v>5.973</v>
       </c>
       <c r="C185" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D185" s="10" t="n">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="E185" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F185" s="16">
@@ -13398,17 +13398,17 @@
     <row r="186">
       <c r="A186" s="10" t="inlineStr">
         <is>
-          <t>db.r6in.8xlarge</t>
+          <t>db.r5.12xlarge</t>
         </is>
       </c>
       <c r="B186" s="46" t="n">
-        <v>5.534</v>
+        <v>6</v>
       </c>
       <c r="C186" s="10" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D186" s="10" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E186" s="10" t="inlineStr">
         <is>
@@ -13427,21 +13427,21 @@
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
         <is>
-          <t>db.m6i.16xlarge</t>
+          <t>db.r6i.12xlarge</t>
         </is>
       </c>
       <c r="B187" s="46" t="n">
-        <v>5.696</v>
+        <v>6</v>
       </c>
       <c r="C187" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D187" s="10" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E187" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F187" s="16">
@@ -13456,11 +13456,11 @@
     <row r="188">
       <c r="A188" s="10" t="inlineStr">
         <is>
-          <t>db.r8g.12xlarge</t>
+          <t>db.r7i.12xlarge</t>
         </is>
       </c>
       <c r="B188" s="46" t="n">
-        <v>5.736</v>
+        <v>6</v>
       </c>
       <c r="C188" s="10" t="n">
         <v>48</v>
@@ -13485,11 +13485,11 @@
     <row r="189">
       <c r="A189" s="10" t="inlineStr">
         <is>
-          <t>db.r7g.12xlarge</t>
+          <t>db.r6gd.12xlarge</t>
         </is>
       </c>
       <c r="B189" s="46" t="n">
-        <v>5.738</v>
+        <v>6.171</v>
       </c>
       <c r="C189" s="10" t="n">
         <v>48</v>
@@ -13514,17 +13514,17 @@
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
         <is>
-          <t>db.m9g.16xlarge</t>
+          <t>db.m6in.12xlarge</t>
         </is>
       </c>
       <c r="B190" s="46" t="n">
-        <v>5.86</v>
+        <v>6.197</v>
       </c>
       <c r="C190" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D190" s="10" t="n">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="E190" s="10" t="inlineStr">
         <is>
@@ -13543,17 +13543,17 @@
     <row r="191">
       <c r="A191" s="10" t="inlineStr">
         <is>
-          <t>db.r5.24xlarge</t>
+          <t>db.r6idn.8xlarge</t>
         </is>
       </c>
       <c r="B191" s="46" t="n">
-        <v>5.952</v>
+        <v>6.203</v>
       </c>
       <c r="C191" s="10" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="D191" s="10" t="n">
-        <v>768</v>
+        <v>256</v>
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
@@ -13572,17 +13572,17 @@
     <row r="192">
       <c r="A192" s="10" t="inlineStr">
         <is>
-          <t>db.r7i.24xlarge</t>
+          <t>db.m8gd.16xlarge</t>
         </is>
       </c>
       <c r="B192" s="46" t="n">
-        <v>5.952</v>
+        <v>6.3232</v>
       </c>
       <c r="C192" s="10" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D192" s="10" t="n">
-        <v>768</v>
+        <v>256</v>
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
@@ -13601,21 +13601,21 @@
     <row r="193">
       <c r="A193" s="10" t="inlineStr">
         <is>
-          <t>db.m6gd.16xlarge</t>
+          <t>db.r8gd.12xlarge</t>
         </is>
       </c>
       <c r="B193" s="46" t="n">
-        <v>5.973</v>
+        <v>6.552</v>
       </c>
       <c r="C193" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D193" s="10" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E193" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F193" s="16">
@@ -13630,21 +13630,21 @@
     <row r="194">
       <c r="A194" s="10" t="inlineStr">
         <is>
-          <t>db.r6i.12xlarge</t>
+          <t>db.m5d.16xlarge</t>
         </is>
       </c>
       <c r="B194" s="46" t="n">
-        <v>6</v>
+        <v>6.705</v>
       </c>
       <c r="C194" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D194" s="10" t="n">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="E194" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F194" s="16">
@@ -13659,11 +13659,11 @@
     <row r="195">
       <c r="A195" s="10" t="inlineStr">
         <is>
-          <t>db.r6gd.12xlarge</t>
+          <t>db.r5d.12xlarge</t>
         </is>
       </c>
       <c r="B195" s="46" t="n">
-        <v>6.171</v>
+        <v>6.857</v>
       </c>
       <c r="C195" s="10" t="n">
         <v>48</v>
@@ -13688,17 +13688,17 @@
     <row r="196">
       <c r="A196" s="10" t="inlineStr">
         <is>
-          <t>db.m6in.12xlarge</t>
+          <t>db.m8a.16xlarge</t>
         </is>
       </c>
       <c r="B196" s="46" t="n">
-        <v>6.197</v>
+        <v>6.8768</v>
       </c>
       <c r="C196" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D196" s="10" t="n">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="E196" s="10" t="inlineStr">
         <is>
@@ -13717,21 +13717,21 @@
     <row r="197">
       <c r="A197" s="10" t="inlineStr">
         <is>
-          <t>db.r6idn.8xlarge</t>
+          <t>db.m6idn.12xlarge</t>
         </is>
       </c>
       <c r="B197" s="46" t="n">
-        <v>6.203</v>
+        <v>7.08</v>
       </c>
       <c r="C197" s="10" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D197" s="10" t="n">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F197" s="16">
@@ -13746,17 +13746,17 @@
     <row r="198">
       <c r="A198" s="10" t="inlineStr">
         <is>
-          <t>db.m8gd.16xlarge</t>
+          <t>db.r5b.12xlarge</t>
         </is>
       </c>
       <c r="B198" s="46" t="n">
-        <v>6.3232</v>
+        <v>7.104</v>
       </c>
       <c r="C198" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D198" s="10" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E198" s="10" t="inlineStr">
         <is>
@@ -13775,11 +13775,11 @@
     <row r="199">
       <c r="A199" s="10" t="inlineStr">
         <is>
-          <t>db.r8gd.12xlarge</t>
+          <t>db.r6id.12xlarge</t>
         </is>
       </c>
       <c r="B199" s="46" t="n">
-        <v>6.552</v>
+        <v>7.157</v>
       </c>
       <c r="C199" s="10" t="n">
         <v>48</v>
@@ -13804,11 +13804,11 @@
     <row r="200">
       <c r="A200" s="10" t="inlineStr">
         <is>
-          <t>db.m5d.16xlarge</t>
+          <t>db.m6id.16xlarge</t>
         </is>
       </c>
       <c r="B200" s="46" t="n">
-        <v>6.705</v>
+        <v>7.174</v>
       </c>
       <c r="C200" s="10" t="n">
         <v>64</v>
@@ -13833,17 +13833,17 @@
     <row r="201">
       <c r="A201" s="10" t="inlineStr">
         <is>
-          <t>db.r5d.12xlarge</t>
+          <t>db.r6g.16xlarge</t>
         </is>
       </c>
       <c r="B201" s="46" t="n">
-        <v>6.857</v>
+        <v>7.194</v>
       </c>
       <c r="C201" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D201" s="10" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
       <c r="E201" s="10" t="inlineStr">
         <is>
@@ -13862,21 +13862,21 @@
     <row r="202">
       <c r="A202" s="10" t="inlineStr">
         <is>
-          <t>db.m8a.16xlarge</t>
+          <t>db.r8a.12xlarge</t>
         </is>
       </c>
       <c r="B202" s="46" t="n">
-        <v>6.8768</v>
+        <v>7.2456</v>
       </c>
       <c r="C202" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D202" s="10" t="n">
-        <v>256</v>
+        <v>384</v>
       </c>
       <c r="E202" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F202" s="16">
@@ -13891,21 +13891,21 @@
     <row r="203">
       <c r="A203" s="10" t="inlineStr">
         <is>
-          <t>db.m6idn.12xlarge</t>
+          <t>db.x2iedn.4xlarge</t>
         </is>
       </c>
       <c r="B203" s="46" t="n">
-        <v>7.08</v>
+        <v>7.608</v>
       </c>
       <c r="C203" s="10" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D203" s="10" t="n">
-        <v>192</v>
+        <v>512</v>
       </c>
       <c r="E203" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F203" s="16">
@@ -13920,17 +13920,17 @@
     <row r="204">
       <c r="A204" s="10" t="inlineStr">
         <is>
-          <t>db.r5b.12xlarge</t>
+          <t>db.r8g.16xlarge</t>
         </is>
       </c>
       <c r="B204" s="46" t="n">
-        <v>7.104</v>
+        <v>7.648</v>
       </c>
       <c r="C204" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D204" s="10" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
       <c r="E204" s="10" t="inlineStr">
         <is>
@@ -13949,17 +13949,17 @@
     <row r="205">
       <c r="A205" s="10" t="inlineStr">
         <is>
-          <t>db.r6id.12xlarge</t>
+          <t>db.r7g.16xlarge</t>
         </is>
       </c>
       <c r="B205" s="46" t="n">
-        <v>7.157</v>
+        <v>7.65</v>
       </c>
       <c r="C205" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D205" s="10" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
       <c r="E205" s="10" t="inlineStr">
         <is>
@@ -13978,21 +13978,21 @@
     <row r="206">
       <c r="A206" s="10" t="inlineStr">
         <is>
-          <t>db.m6id.16xlarge</t>
+          <t>db.x2g.12xlarge</t>
         </is>
       </c>
       <c r="B206" s="46" t="n">
-        <v>7.174</v>
+        <v>7.824</v>
       </c>
       <c r="C206" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D206" s="10" t="n">
-        <v>256</v>
+        <v>768</v>
       </c>
       <c r="E206" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F206" s="16">
@@ -14007,11 +14007,11 @@
     <row r="207">
       <c r="A207" s="10" t="inlineStr">
         <is>
-          <t>db.r6g.16xlarge</t>
+          <t>db.r5.16xlarge</t>
         </is>
       </c>
       <c r="B207" s="46" t="n">
-        <v>7.194</v>
+        <v>8</v>
       </c>
       <c r="C207" s="10" t="n">
         <v>64</v>
@@ -14036,17 +14036,17 @@
     <row r="208">
       <c r="A208" s="10" t="inlineStr">
         <is>
-          <t>db.r8a.12xlarge</t>
+          <t>db.r6i.16xlarge</t>
         </is>
       </c>
       <c r="B208" s="46" t="n">
-        <v>7.2456</v>
+        <v>8</v>
       </c>
       <c r="C208" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D208" s="10" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
       <c r="E208" s="10" t="inlineStr">
         <is>
@@ -14065,14 +14065,14 @@
     <row r="209">
       <c r="A209" s="10" t="inlineStr">
         <is>
-          <t>db.x2iedn.4xlarge</t>
+          <t>db.r7i.16xlarge</t>
         </is>
       </c>
       <c r="B209" s="46" t="n">
-        <v>7.608</v>
+        <v>8</v>
       </c>
       <c r="C209" s="10" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D209" s="10" t="n">
         <v>512</v>
@@ -14094,21 +14094,21 @@
     <row r="210">
       <c r="A210" s="10" t="inlineStr">
         <is>
-          <t>db.r8g.16xlarge</t>
+          <t>db.m8g.24xlarge</t>
         </is>
       </c>
       <c r="B210" s="46" t="n">
-        <v>7.648</v>
+        <v>8.064</v>
       </c>
       <c r="C210" s="10" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D210" s="10" t="n">
         <v>512</v>
       </c>
       <c r="E210" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F210" s="16">
@@ -14123,11 +14123,11 @@
     <row r="211">
       <c r="A211" s="10" t="inlineStr">
         <is>
-          <t>db.r7g.16xlarge</t>
+          <t>db.r6gd.16xlarge</t>
         </is>
       </c>
       <c r="B211" s="46" t="n">
-        <v>7.65</v>
+        <v>8.228999999999999</v>
       </c>
       <c r="C211" s="10" t="n">
         <v>64</v>
@@ -14152,21 +14152,21 @@
     <row r="212">
       <c r="A212" s="10" t="inlineStr">
         <is>
-          <t>db.x2g.12xlarge</t>
+          <t>db.m6in.16xlarge</t>
         </is>
       </c>
       <c r="B212" s="46" t="n">
-        <v>7.824</v>
+        <v>8.262</v>
       </c>
       <c r="C212" s="10" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D212" s="10" t="n">
-        <v>768</v>
+        <v>256</v>
       </c>
       <c r="E212" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F212" s="16">
@@ -14181,21 +14181,21 @@
     <row r="213">
       <c r="A213" s="10" t="inlineStr">
         <is>
-          <t>db.m7i.48xlarge</t>
+          <t>db.r6in.12xlarge</t>
         </is>
       </c>
       <c r="B213" s="46" t="n">
-        <v>7.872</v>
+        <v>8.302</v>
       </c>
       <c r="C213" s="10" t="n">
-        <v>192</v>
+        <v>48</v>
       </c>
       <c r="D213" s="10" t="n">
-        <v>768</v>
+        <v>384</v>
       </c>
       <c r="E213" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F213" s="16">
@@ -14210,21 +14210,21 @@
     <row r="214">
       <c r="A214" s="10" t="inlineStr">
         <is>
-          <t>db.r6i.16xlarge</t>
+          <t>db.m5.24xlarge</t>
         </is>
       </c>
       <c r="B214" s="46" t="n">
-        <v>8</v>
+        <v>8.544</v>
       </c>
       <c r="C214" s="10" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D214" s="10" t="n">
-        <v>512</v>
+        <v>384</v>
       </c>
       <c r="E214" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F214" s="16">
@@ -14239,17 +14239,17 @@
     <row r="215">
       <c r="A215" s="10" t="inlineStr">
         <is>
-          <t>db.m8g.24xlarge</t>
+          <t>db.m6i.24xlarge</t>
         </is>
       </c>
       <c r="B215" s="46" t="n">
-        <v>8.064</v>
+        <v>8.544</v>
       </c>
       <c r="C215" s="10" t="n">
         <v>96</v>
       </c>
       <c r="D215" s="10" t="n">
-        <v>512</v>
+        <v>384</v>
       </c>
       <c r="E215" s="10" t="inlineStr">
         <is>
@@ -14268,21 +14268,21 @@
     <row r="216">
       <c r="A216" s="10" t="inlineStr">
         <is>
-          <t>db.r6gd.16xlarge</t>
+          <t>db.m7i.24xlarge</t>
         </is>
       </c>
       <c r="B216" s="46" t="n">
-        <v>8.228999999999999</v>
+        <v>8.544</v>
       </c>
       <c r="C216" s="10" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D216" s="10" t="n">
-        <v>512</v>
+        <v>384</v>
       </c>
       <c r="E216" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F216" s="16">
@@ -14297,21 +14297,21 @@
     <row r="217">
       <c r="A217" s="10" t="inlineStr">
         <is>
-          <t>db.m6in.16xlarge</t>
+          <t>db.r8gd.16xlarge</t>
         </is>
       </c>
       <c r="B217" s="46" t="n">
-        <v>8.262</v>
+        <v>8.736000000000001</v>
       </c>
       <c r="C217" s="10" t="n">
         <v>64</v>
       </c>
       <c r="D217" s="10" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="E217" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F217" s="16">
@@ -14326,21 +14326,21 @@
     <row r="218">
       <c r="A218" s="10" t="inlineStr">
         <is>
-          <t>db.r6in.12xlarge</t>
+          <t>db.m9g.24xlarge</t>
         </is>
       </c>
       <c r="B218" s="46" t="n">
-        <v>8.302</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C218" s="10" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D218" s="10" t="n">
         <v>384</v>
       </c>
       <c r="E218" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F218" s="16">
@@ -14355,21 +14355,21 @@
     <row r="219">
       <c r="A219" s="10" t="inlineStr">
         <is>
-          <t>db.m6i.24xlarge</t>
+          <t>db.r5d.16xlarge</t>
         </is>
       </c>
       <c r="B219" s="46" t="n">
-        <v>8.544</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="C219" s="10" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D219" s="10" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
       <c r="E219" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F219" s="16">
@@ -14384,17 +14384,17 @@
     <row r="220">
       <c r="A220" s="10" t="inlineStr">
         <is>
-          <t>db.r8gd.16xlarge</t>
+          <t>db.r6idn.12xlarge</t>
         </is>
       </c>
       <c r="B220" s="46" t="n">
-        <v>8.736000000000001</v>
+        <v>9.304</v>
       </c>
       <c r="C220" s="10" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D220" s="10" t="n">
-        <v>512</v>
+        <v>384</v>
       </c>
       <c r="E220" s="10" t="inlineStr">
         <is>
@@ -14413,17 +14413,17 @@
     <row r="221">
       <c r="A221" s="10" t="inlineStr">
         <is>
-          <t>db.m9g.24xlarge</t>
+          <t>db.m6idn.16xlarge</t>
         </is>
       </c>
       <c r="B221" s="46" t="n">
-        <v>8.789999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="C221" s="10" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D221" s="10" t="n">
-        <v>384</v>
+        <v>256</v>
       </c>
       <c r="E221" s="10" t="inlineStr">
         <is>
@@ -14442,11 +14442,11 @@
     <row r="222">
       <c r="A222" s="10" t="inlineStr">
         <is>
-          <t>db.r5d.16xlarge</t>
+          <t>db.r5b.16xlarge</t>
         </is>
       </c>
       <c r="B222" s="46" t="n">
-        <v>9.143000000000001</v>
+        <v>9.472</v>
       </c>
       <c r="C222" s="10" t="n">
         <v>64</v>
@@ -14471,14 +14471,14 @@
     <row r="223">
       <c r="A223" s="10" t="inlineStr">
         <is>
-          <t>db.r6idn.12xlarge</t>
+          <t>db.m8gd.24xlarge</t>
         </is>
       </c>
       <c r="B223" s="46" t="n">
-        <v>9.304</v>
+        <v>9.4848</v>
       </c>
       <c r="C223" s="10" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D223" s="10" t="n">
         <v>384</v>
@@ -14500,21 +14500,21 @@
     <row r="224">
       <c r="A224" s="10" t="inlineStr">
         <is>
-          <t>db.m6idn.16xlarge</t>
+          <t>db.r6id.16xlarge</t>
         </is>
       </c>
       <c r="B224" s="46" t="n">
-        <v>9.44</v>
+        <v>9.542999999999999</v>
       </c>
       <c r="C224" s="10" t="n">
         <v>64</v>
       </c>
       <c r="D224" s="10" t="n">
-        <v>256</v>
+        <v>512</v>
       </c>
       <c r="E224" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F224" s="16">
@@ -14529,11 +14529,11 @@
     <row r="225">
       <c r="A225" s="10" t="inlineStr">
         <is>
-          <t>db.r5b.16xlarge</t>
+          <t>db.r8a.16xlarge</t>
         </is>
       </c>
       <c r="B225" s="46" t="n">
-        <v>9.472</v>
+        <v>9.6608</v>
       </c>
       <c r="C225" s="10" t="n">
         <v>64</v>
@@ -14558,11 +14558,11 @@
     <row r="226">
       <c r="A226" s="10" t="inlineStr">
         <is>
-          <t>db.m8gd.24xlarge</t>
+          <t>db.m5d.24xlarge</t>
         </is>
       </c>
       <c r="B226" s="46" t="n">
-        <v>9.4848</v>
+        <v>10.057</v>
       </c>
       <c r="C226" s="10" t="n">
         <v>96</v>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="E226" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F226" s="16">
@@ -14587,21 +14587,21 @@
     <row r="227">
       <c r="A227" s="10" t="inlineStr">
         <is>
-          <t>db.r6id.16xlarge</t>
+          <t>db.m8a.24xlarge</t>
         </is>
       </c>
       <c r="B227" s="46" t="n">
-        <v>9.542999999999999</v>
+        <v>10.3152</v>
       </c>
       <c r="C227" s="10" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D227" s="10" t="n">
-        <v>512</v>
+        <v>384</v>
       </c>
       <c r="E227" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F227" s="16">
@@ -14616,17 +14616,17 @@
     <row r="228">
       <c r="A228" s="10" t="inlineStr">
         <is>
-          <t>db.r8a.16xlarge</t>
+          <t>db.x2g.16xlarge</t>
         </is>
       </c>
       <c r="B228" s="46" t="n">
-        <v>9.6608</v>
+        <v>10.432</v>
       </c>
       <c r="C228" s="10" t="n">
         <v>64</v>
       </c>
       <c r="D228" s="10" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="E228" s="10" t="inlineStr">
         <is>
@@ -14645,11 +14645,11 @@
     <row r="229">
       <c r="A229" s="10" t="inlineStr">
         <is>
-          <t>db.m5d.24xlarge</t>
+          <t>db.m6id.24xlarge</t>
         </is>
       </c>
       <c r="B229" s="46" t="n">
-        <v>10.057</v>
+        <v>10.761</v>
       </c>
       <c r="C229" s="10" t="n">
         <v>96</v>
@@ -14674,21 +14674,21 @@
     <row r="230">
       <c r="A230" s="10" t="inlineStr">
         <is>
-          <t>db.m8a.24xlarge</t>
+          <t>db.r6in.16xlarge</t>
         </is>
       </c>
       <c r="B230" s="46" t="n">
-        <v>10.3152</v>
+        <v>11.069</v>
       </c>
       <c r="C230" s="10" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D230" s="10" t="n">
-        <v>384</v>
+        <v>512</v>
       </c>
       <c r="E230" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F230" s="16">
@@ -14703,21 +14703,21 @@
     <row r="231">
       <c r="A231" s="10" t="inlineStr">
         <is>
-          <t>db.x2g.16xlarge</t>
+          <t>db.m6i.32xlarge</t>
         </is>
       </c>
       <c r="B231" s="46" t="n">
-        <v>10.432</v>
+        <v>11.392</v>
       </c>
       <c r="C231" s="10" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="D231" s="10" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="E231" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F231" s="16">
@@ -14732,21 +14732,21 @@
     <row r="232">
       <c r="A232" s="10" t="inlineStr">
         <is>
-          <t>db.m6id.24xlarge</t>
+          <t>db.r8g.24xlarge</t>
         </is>
       </c>
       <c r="B232" s="46" t="n">
-        <v>10.761</v>
+        <v>11.472</v>
       </c>
       <c r="C232" s="10" t="n">
         <v>96</v>
       </c>
       <c r="D232" s="10" t="n">
-        <v>384</v>
+        <v>768</v>
       </c>
       <c r="E232" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F232" s="16">
@@ -14761,17 +14761,17 @@
     <row r="233">
       <c r="A233" s="10" t="inlineStr">
         <is>
-          <t>db.r6in.16xlarge</t>
+          <t>db.r5.24xlarge</t>
         </is>
       </c>
       <c r="B233" s="46" t="n">
-        <v>11.069</v>
+        <v>12</v>
       </c>
       <c r="C233" s="10" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D233" s="10" t="n">
-        <v>512</v>
+        <v>768</v>
       </c>
       <c r="E233" s="10" t="inlineStr">
         <is>
@@ -14790,21 +14790,21 @@
     <row r="234">
       <c r="A234" s="10" t="inlineStr">
         <is>
-          <t>db.m6i.32xlarge</t>
+          <t>db.r6i.24xlarge</t>
         </is>
       </c>
       <c r="B234" s="46" t="n">
-        <v>11.392</v>
+        <v>12</v>
       </c>
       <c r="C234" s="10" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D234" s="10" t="n">
-        <v>512</v>
+        <v>768</v>
       </c>
       <c r="E234" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F234" s="16">
@@ -14819,11 +14819,11 @@
     <row r="235">
       <c r="A235" s="10" t="inlineStr">
         <is>
-          <t>db.r8g.24xlarge</t>
+          <t>db.r7i.24xlarge</t>
         </is>
       </c>
       <c r="B235" s="46" t="n">
-        <v>11.472</v>
+        <v>12</v>
       </c>
       <c r="C235" s="10" t="n">
         <v>96</v>
@@ -14848,21 +14848,21 @@
     <row r="236">
       <c r="A236" s="10" t="inlineStr">
         <is>
-          <t>db.r7i.48xlarge</t>
+          <t>db.m6in.24xlarge</t>
         </is>
       </c>
       <c r="B236" s="46" t="n">
-        <v>11.904</v>
+        <v>12.394</v>
       </c>
       <c r="C236" s="10" t="n">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="D236" s="10" t="n">
-        <v>1536</v>
+        <v>384</v>
       </c>
       <c r="E236" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F236" s="16">
@@ -14877,17 +14877,17 @@
     <row r="237">
       <c r="A237" s="10" t="inlineStr">
         <is>
-          <t>db.r6i.24xlarge</t>
+          <t>db.r6idn.16xlarge</t>
         </is>
       </c>
       <c r="B237" s="46" t="n">
-        <v>12</v>
+        <v>12.405</v>
       </c>
       <c r="C237" s="10" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D237" s="10" t="n">
-        <v>768</v>
+        <v>512</v>
       </c>
       <c r="E237" s="10" t="inlineStr">
         <is>
@@ -14906,21 +14906,21 @@
     <row r="238">
       <c r="A238" s="10" t="inlineStr">
         <is>
-          <t>db.m6in.24xlarge</t>
+          <t>db.r8gd.24xlarge</t>
         </is>
       </c>
       <c r="B238" s="46" t="n">
-        <v>12.394</v>
+        <v>13.104</v>
       </c>
       <c r="C238" s="10" t="n">
         <v>96</v>
       </c>
       <c r="D238" s="10" t="n">
-        <v>384</v>
+        <v>768</v>
       </c>
       <c r="E238" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F238" s="16">
@@ -14935,17 +14935,17 @@
     <row r="239">
       <c r="A239" s="10" t="inlineStr">
         <is>
-          <t>db.r6idn.16xlarge</t>
+          <t>db.r5d.24xlarge</t>
         </is>
       </c>
       <c r="B239" s="46" t="n">
-        <v>12.405</v>
+        <v>13.714</v>
       </c>
       <c r="C239" s="10" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="D239" s="10" t="n">
-        <v>512</v>
+        <v>768</v>
       </c>
       <c r="E239" s="10" t="inlineStr">
         <is>
@@ -14964,21 +14964,21 @@
     <row r="240">
       <c r="A240" s="10" t="inlineStr">
         <is>
-          <t>db.r8gd.24xlarge</t>
+          <t>db.m6idn.24xlarge</t>
         </is>
       </c>
       <c r="B240" s="46" t="n">
-        <v>13.104</v>
+        <v>14.16</v>
       </c>
       <c r="C240" s="10" t="n">
         <v>96</v>
       </c>
       <c r="D240" s="10" t="n">
-        <v>768</v>
+        <v>384</v>
       </c>
       <c r="E240" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F240" s="16">
@@ -14993,11 +14993,11 @@
     <row r="241">
       <c r="A241" s="10" t="inlineStr">
         <is>
-          <t>db.r5d.24xlarge</t>
+          <t>db.r5b.24xlarge</t>
         </is>
       </c>
       <c r="B241" s="46" t="n">
-        <v>13.714</v>
+        <v>14.208</v>
       </c>
       <c r="C241" s="10" t="n">
         <v>96</v>
@@ -15022,21 +15022,21 @@
     <row r="242">
       <c r="A242" s="10" t="inlineStr">
         <is>
-          <t>db.m6idn.24xlarge</t>
+          <t>db.r6id.24xlarge</t>
         </is>
       </c>
       <c r="B242" s="46" t="n">
-        <v>14.16</v>
+        <v>14.314</v>
       </c>
       <c r="C242" s="10" t="n">
         <v>96</v>
       </c>
       <c r="D242" s="10" t="n">
-        <v>384</v>
+        <v>768</v>
       </c>
       <c r="E242" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F242" s="16">
@@ -15051,21 +15051,21 @@
     <row r="243">
       <c r="A243" s="10" t="inlineStr">
         <is>
-          <t>db.r5b.24xlarge</t>
+          <t>db.m6id.32xlarge</t>
         </is>
       </c>
       <c r="B243" s="46" t="n">
-        <v>14.208</v>
+        <v>14.349</v>
       </c>
       <c r="C243" s="10" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D243" s="10" t="n">
-        <v>768</v>
+        <v>512</v>
       </c>
       <c r="E243" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F243" s="16">
@@ -15080,11 +15080,11 @@
     <row r="244">
       <c r="A244" s="10" t="inlineStr">
         <is>
-          <t>db.r6id.24xlarge</t>
+          <t>db.r8a.24xlarge</t>
         </is>
       </c>
       <c r="B244" s="46" t="n">
-        <v>14.314</v>
+        <v>14.4912</v>
       </c>
       <c r="C244" s="10" t="n">
         <v>96</v>
@@ -15109,21 +15109,21 @@
     <row r="245">
       <c r="A245" s="10" t="inlineStr">
         <is>
-          <t>db.m6id.32xlarge</t>
+          <t>db.x2iedn.8xlarge</t>
         </is>
       </c>
       <c r="B245" s="46" t="n">
-        <v>14.349</v>
+        <v>15.216</v>
       </c>
       <c r="C245" s="10" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="D245" s="10" t="n">
-        <v>512</v>
+        <v>1024</v>
       </c>
       <c r="E245" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F245" s="16">
@@ -15138,17 +15138,17 @@
     <row r="246">
       <c r="A246" s="10" t="inlineStr">
         <is>
-          <t>db.r8a.24xlarge</t>
+          <t>db.r6i.32xlarge</t>
         </is>
       </c>
       <c r="B246" s="46" t="n">
-        <v>14.4912</v>
+        <v>16</v>
       </c>
       <c r="C246" s="10" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D246" s="10" t="n">
-        <v>768</v>
+        <v>1024</v>
       </c>
       <c r="E246" s="10" t="inlineStr">
         <is>
@@ -15167,21 +15167,21 @@
     <row r="247">
       <c r="A247" s="10" t="inlineStr">
         <is>
-          <t>db.x2iedn.8xlarge</t>
+          <t>db.m8g.48xlarge</t>
         </is>
       </c>
       <c r="B247" s="46" t="n">
-        <v>15.216</v>
+        <v>16.128</v>
       </c>
       <c r="C247" s="10" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D247" s="10" t="n">
-        <v>1024</v>
+        <v>768</v>
       </c>
       <c r="E247" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F247" s="16">
@@ -15196,21 +15196,21 @@
     <row r="248">
       <c r="A248" s="10" t="inlineStr">
         <is>
-          <t>db.r6i.32xlarge</t>
+          <t>db.m6in.32xlarge</t>
         </is>
       </c>
       <c r="B248" s="46" t="n">
-        <v>16</v>
+        <v>16.525</v>
       </c>
       <c r="C248" s="10" t="n">
         <v>128</v>
       </c>
       <c r="D248" s="10" t="n">
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="E248" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F248" s="16">
@@ -15225,21 +15225,21 @@
     <row r="249">
       <c r="A249" s="10" t="inlineStr">
         <is>
-          <t>db.m8g.48xlarge</t>
+          <t>db.r6in.24xlarge</t>
         </is>
       </c>
       <c r="B249" s="46" t="n">
-        <v>16.128</v>
+        <v>16.603</v>
       </c>
       <c r="C249" s="10" t="n">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="D249" s="10" t="n">
         <v>768</v>
       </c>
       <c r="E249" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F249" s="16">
@@ -15254,17 +15254,17 @@
     <row r="250">
       <c r="A250" s="10" t="inlineStr">
         <is>
-          <t>db.m6in.32xlarge</t>
+          <t>db.m7i.48xlarge</t>
         </is>
       </c>
       <c r="B250" s="46" t="n">
-        <v>16.525</v>
+        <v>17.088</v>
       </c>
       <c r="C250" s="10" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="D250" s="10" t="n">
-        <v>512</v>
+        <v>768</v>
       </c>
       <c r="E250" s="10" t="inlineStr">
         <is>
@@ -15283,21 +15283,21 @@
     <row r="251">
       <c r="A251" s="10" t="inlineStr">
         <is>
-          <t>db.r6in.24xlarge</t>
+          <t>db.m9g.48xlarge</t>
         </is>
       </c>
       <c r="B251" s="46" t="n">
-        <v>16.603</v>
+        <v>17.58</v>
       </c>
       <c r="C251" s="10" t="n">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="D251" s="10" t="n">
         <v>768</v>
       </c>
       <c r="E251" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F251" s="16">
@@ -15312,21 +15312,21 @@
     <row r="252">
       <c r="A252" s="10" t="inlineStr">
         <is>
-          <t>db.m9g.48xlarge</t>
+          <t>db.r6idn.24xlarge</t>
         </is>
       </c>
       <c r="B252" s="46" t="n">
-        <v>17.58</v>
+        <v>18.608</v>
       </c>
       <c r="C252" s="10" t="n">
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="D252" s="10" t="n">
         <v>768</v>
       </c>
       <c r="E252" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F252" s="16">
@@ -15341,21 +15341,21 @@
     <row r="253">
       <c r="A253" s="10" t="inlineStr">
         <is>
-          <t>db.r6idn.24xlarge</t>
+          <t>db.m6idn.32xlarge</t>
         </is>
       </c>
       <c r="B253" s="46" t="n">
-        <v>18.608</v>
+        <v>18.88</v>
       </c>
       <c r="C253" s="10" t="n">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D253" s="10" t="n">
-        <v>768</v>
+        <v>512</v>
       </c>
       <c r="E253" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F253" s="16">
@@ -15370,21 +15370,21 @@
     <row r="254">
       <c r="A254" s="10" t="inlineStr">
         <is>
-          <t>db.m6idn.32xlarge</t>
+          <t>db.m8gd.48xlarge</t>
         </is>
       </c>
       <c r="B254" s="46" t="n">
-        <v>18.88</v>
+        <v>18.9696</v>
       </c>
       <c r="C254" s="10" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="D254" s="10" t="n">
-        <v>512</v>
+        <v>768</v>
       </c>
       <c r="E254" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F254" s="16">
@@ -15399,17 +15399,17 @@
     <row r="255">
       <c r="A255" s="10" t="inlineStr">
         <is>
-          <t>db.m8gd.48xlarge</t>
+          <t>db.r6id.32xlarge</t>
         </is>
       </c>
       <c r="B255" s="46" t="n">
-        <v>18.9696</v>
+        <v>19.086</v>
       </c>
       <c r="C255" s="10" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="D255" s="10" t="n">
-        <v>768</v>
+        <v>1024</v>
       </c>
       <c r="E255" s="10" t="inlineStr">
         <is>
@@ -15428,21 +15428,21 @@
     <row r="256">
       <c r="A256" s="10" t="inlineStr">
         <is>
-          <t>db.r6id.32xlarge</t>
+          <t>db.m8a.48xlarge</t>
         </is>
       </c>
       <c r="B256" s="46" t="n">
-        <v>19.086</v>
+        <v>20.6304</v>
       </c>
       <c r="C256" s="10" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="D256" s="10" t="n">
-        <v>1024</v>
+        <v>768</v>
       </c>
       <c r="E256" s="10" t="inlineStr">
         <is>
-          <t>Memory optimized</t>
+          <t>General purpose</t>
         </is>
       </c>
       <c r="F256" s="16">
@@ -15457,21 +15457,21 @@
     <row r="257">
       <c r="A257" s="10" t="inlineStr">
         <is>
-          <t>db.m8a.48xlarge</t>
+          <t>db.r6in.32xlarge</t>
         </is>
       </c>
       <c r="B257" s="46" t="n">
-        <v>20.6304</v>
+        <v>22.138</v>
       </c>
       <c r="C257" s="10" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="D257" s="10" t="n">
-        <v>768</v>
+        <v>1024</v>
       </c>
       <c r="E257" s="10" t="inlineStr">
         <is>
-          <t>General purpose</t>
+          <t>Memory optimized</t>
         </is>
       </c>
       <c r="F257" s="16">
@@ -15486,17 +15486,17 @@
     <row r="258">
       <c r="A258" s="10" t="inlineStr">
         <is>
-          <t>db.r6in.32xlarge</t>
+          <t>db.r8g.48xlarge</t>
         </is>
       </c>
       <c r="B258" s="46" t="n">
-        <v>22.138</v>
+        <v>22.944</v>
       </c>
       <c r="C258" s="10" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="D258" s="10" t="n">
-        <v>1024</v>
+        <v>1536</v>
       </c>
       <c r="E258" s="10" t="inlineStr">
         <is>
@@ -15515,11 +15515,11 @@
     <row r="259">
       <c r="A259" s="10" t="inlineStr">
         <is>
-          <t>db.r8g.48xlarge</t>
+          <t>db.r7i.48xlarge</t>
         </is>
       </c>
       <c r="B259" s="46" t="n">
-        <v>22.944</v>
+        <v>24</v>
       </c>
       <c r="C259" s="10" t="n">
         <v>192</v>
